--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6021-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6021-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D95C53D-F345-421D-BBB2-940C79CA1F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D60211A9-0DE9-4A39-B645-89B8D971431D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{AD938E27-24B4-471D-8DC3-A77B64B66AEC}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{2F213DFA-20D1-4C49-9833-18A12BDF8084}"/>
   </bookViews>
   <sheets>
     <sheet name="6021-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1565,27 +1565,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9668AE7-B02E-45F6-B372-17F716BCDA6C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{082E95CA-4ED2-478A-A27A-8CE3AAC125C1}">
   <dimension ref="A1:X40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="9" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1619,7 +1619,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1655,7 +1655,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1775,7 +1775,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2025</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="41">
         <v>2024</v>
       </c>
@@ -1993,7 +1993,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>9.41</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>4.1399999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2023</v>
       </c>
@@ -2213,7 +2213,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2287,7 +2287,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2361,7 +2361,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="41">
         <v>2022</v>
       </c>
@@ -2433,7 +2433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2021</v>
       </c>
@@ -2505,7 +2505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="41">
         <v>2020</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2019</v>
       </c>
@@ -2649,7 +2649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="41">
         <v>2018</v>
       </c>
@@ -2721,7 +2721,7 @@
         <v>9.52</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2017</v>
       </c>
@@ -2793,7 +2793,7 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="41">
         <v>2016</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>2015</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="41">
         <v>2014</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2013</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>5.47</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="41">
         <v>2012</v>
       </c>
@@ -3153,7 +3153,7 @@
         <v>3.54</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <v>2011</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="43">
         <v>2010</v>
       </c>
@@ -3297,7 +3297,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="45"/>
       <c r="B26" s="46"/>
       <c r="C26" s="20" t="s">
@@ -3325,7 +3325,7 @@
       <c r="W26" s="52"/>
       <c r="X26" s="48"/>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="39">
         <v>2009</v>
       </c>
@@ -3397,7 +3397,7 @@
         <v>3.76</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="41">
         <v>2008</v>
       </c>
@@ -3469,7 +3469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
         <v>2007</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="43">
         <v>2006</v>
       </c>
@@ -3613,7 +3613,7 @@
         <v>8.16</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="45"/>
       <c r="B31" s="46"/>
       <c r="C31" s="20" t="s">
@@ -3641,7 +3641,7 @@
       <c r="W31" s="52"/>
       <c r="X31" s="48"/>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="53">
         <v>2005</v>
       </c>
@@ -3713,7 +3713,7 @@
         <v>6.35</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="55"/>
       <c r="B33" s="56"/>
       <c r="C33" s="22" t="s">
@@ -3741,7 +3741,7 @@
       <c r="W33" s="62"/>
       <c r="X33" s="58"/>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="41">
         <v>2004</v>
       </c>
@@ -3813,7 +3813,7 @@
         <v>7.22</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="39">
         <v>2003</v>
       </c>
@@ -3885,7 +3885,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="41">
         <v>2002</v>
       </c>
@@ -3957,7 +3957,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="39">
         <v>2001</v>
       </c>
@@ -4029,7 +4029,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="41">
         <v>2000</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="39">
         <v>1999</v>
       </c>
@@ -4173,7 +4173,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="41" t="s">
         <v>52</v>
       </c>
